--- a/Regionalized FeliX/Model Files/InitialValues.xlsx
+++ b/Regionalized FeliX/Model Files/InitialValues.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1240" documentId="13_ncr:1_{28C6C791-891C-49C6-B485-EBA1BBBF38AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{489CE2D8-5557-4E08-90DF-EBE422DB1238}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5856" yWindow="2124" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stocks" sheetId="1" r:id="rId1"/>
@@ -1485,7 +1485,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1818,12 +1818,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="44">
@@ -30033,7 +30027,7 @@
         <v>952653.84063279699</v>
       </c>
       <c r="L266" s="14">
-        <f t="shared" ref="L266:L281" si="97">Y243/Y290*L31*Y266*$E$282</f>
+        <f t="shared" ref="L266:L280" si="97">Y243/Y290*L31*Y266*$E$282</f>
         <v>67878.134341032972</v>
       </c>
       <c r="P266" s="73">

--- a/Regionalized FeliX/Model Files/InitialValues.xlsx
+++ b/Regionalized FeliX/Model Files/InitialValues.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1240" documentId="13_ncr:1_{28C6C791-891C-49C6-B485-EBA1BBBF38AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{489CE2D8-5557-4E08-90DF-EBE422DB1238}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5856" yWindow="2124" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="936" yWindow="2100" windowWidth="17280" windowHeight="8880" tabRatio="623" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stocks" sheetId="1" r:id="rId1"/>
